--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.03815</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.072003</v>
+        <v>0.042342</v>
       </c>
       <c r="C3" t="n">
-        <v>1.068872</v>
+        <v>1.109873</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.068312</v>
+        <v>0.040528</v>
       </c>
       <c r="C4" t="n">
-        <v>0.948727</v>
+        <v>0.957152</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.042342</v>
+        <v>0.042258</v>
       </c>
       <c r="C3" t="n">
-        <v>1.109873</v>
+        <v>1.107673</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.040528</v>
+        <v>0.040507</v>
       </c>
       <c r="C4" t="n">
-        <v>0.957152</v>
+        <v>0.958568</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.042258</v>
+        <v>0.04191</v>
       </c>
       <c r="C3" t="n">
-        <v>1.107673</v>
+        <v>1.09854</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.040507</v>
+        <v>0.03971</v>
       </c>
       <c r="C4" t="n">
-        <v>0.958568</v>
+        <v>0.947508</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04191</v>
+        <v>0.041903</v>
       </c>
       <c r="C3" t="n">
-        <v>1.09854</v>
+        <v>1.098378</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03971</v>
+        <v>0.03956</v>
       </c>
       <c r="C4" t="n">
-        <v>0.947508</v>
+        <v>0.94408</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.041903</v>
+        <v>0.041816</v>
       </c>
       <c r="C3" t="n">
-        <v>1.098378</v>
+        <v>1.0961</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03956</v>
+        <v>0.039359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.94408</v>
+        <v>0.941249</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03815</v>
+        <v>0.054595</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.041816</v>
+        <v>0.05864</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0961</v>
+        <v>1.074077</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039359</v>
+        <v>0.053812</v>
       </c>
       <c r="C4" t="n">
-        <v>0.941249</v>
+        <v>0.917679</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05864</v>
+        <v>0.05866</v>
       </c>
       <c r="C3" t="n">
-        <v>1.074077</v>
+        <v>1.074455</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.053812</v>
+        <v>0.053998</v>
       </c>
       <c r="C4" t="n">
-        <v>0.917679</v>
+        <v>0.920517</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.054595</v>
+        <v>0.01417</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05866</v>
+        <v>0.014118</v>
       </c>
       <c r="C3" t="n">
-        <v>1.074455</v>
+        <v>0.9963</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.053998</v>
+        <v>0.011951</v>
       </c>
       <c r="C4" t="n">
-        <v>0.920517</v>
+        <v>0.846496</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>0.014118</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9963</v>
+        <v>0.996333</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.011951</v>
+        <v>0.012058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.846496</v>
+        <v>0.854106</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01417</v>
+        <v>0.03815</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.014118</v>
+        <v>0.041421</v>
       </c>
       <c r="C3" t="n">
-        <v>0.996333</v>
+        <v>1.08574</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012058</v>
+        <v>0.038846</v>
       </c>
       <c r="C4" t="n">
-        <v>0.854106</v>
+        <v>0.937841</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03815</v>
+        <v>0.008333999999999999</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.041421</v>
+        <v>0.009042</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08574</v>
+        <v>1.084921</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.038846</v>
+        <v>0.008439</v>
       </c>
       <c r="C4" t="n">
-        <v>0.937841</v>
+        <v>0.93333</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009042</v>
+        <v>0.008965000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>1.084921</v>
+        <v>1.075676</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008439</v>
+        <v>0.008404</v>
       </c>
       <c r="C4" t="n">
-        <v>0.93333</v>
+        <v>0.937422</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008965000000000001</v>
+        <v>0.008966</v>
       </c>
       <c r="C3" t="n">
-        <v>1.075676</v>
+        <v>1.075752</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008404</v>
+        <v>0.008402</v>
       </c>
       <c r="C4" t="n">
-        <v>0.937422</v>
+        <v>0.937149</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008966</v>
+        <v>0.008944000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>1.075752</v>
+        <v>1.07319</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008402</v>
+        <v>0.008444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.937149</v>
+        <v>0.944044</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008944000000000001</v>
+        <v>0.008951000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>1.07319</v>
+        <v>1.073984</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008444</v>
+        <v>0.008449</v>
       </c>
       <c r="C4" t="n">
-        <v>0.944044</v>
+        <v>0.943918</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008951000000000001</v>
+        <v>0.008952</v>
       </c>
       <c r="C3" t="n">
-        <v>1.073984</v>
+        <v>1.074134</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008449</v>
+        <v>0.008418999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.943918</v>
+        <v>0.940437</v>
       </c>
     </row>
   </sheetData>
